--- a/Result/profitability/1609.xlsx
+++ b/Result/profitability/1609.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.06</v>
       </c>
       <c r="M2" t="n">
-        <v>0.35375</v>
+        <v>0.51</v>
       </c>
       <c r="N2" t="n">
-        <v>13.755</v>
+        <v>14.33</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0.38</v>
       </c>
       <c r="M3" t="n">
-        <v>0.36</v>
+        <v>0.52625</v>
       </c>
       <c r="N3" t="n">
-        <v>13.01875</v>
+        <v>13.44125</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.09</v>
       </c>
       <c r="M4" t="n">
-        <v>0.34</v>
+        <v>0.54875</v>
       </c>
       <c r="N4" t="n">
-        <v>11.5175</v>
+        <v>12.04125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.9</v>
       </c>
       <c r="M5" t="n">
-        <v>0.11375</v>
+        <v>0.1525</v>
       </c>
       <c r="N5" t="n">
-        <v>5.949999999999999</v>
+        <v>6.40375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.25</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.07624999999999998</v>
+        <v>0.06625</v>
       </c>
       <c r="N6" t="n">
-        <v>4.319999999999999</v>
+        <v>5.003749999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>-0.03</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.135</v>
+        <v>0.05875</v>
       </c>
       <c r="N7" t="n">
-        <v>3.54875</v>
+        <v>4.165</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.36</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.09374999999999999</v>
+        <v>0.02124999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>2.85125</v>
+        <v>2.8125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1609</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>9423</v>
+      </c>
+      <c r="D75" t="n">
+        <v>7676</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1747</v>
+      </c>
+      <c r="F75" t="n">
+        <v>18.54</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1125</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>11.94%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>441</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1565</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1240</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.5587500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>15.30375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.393939393939394</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.3100000000000023</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.01644562334217514</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.3100000000000001</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.2440944881889764</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.629999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2434607645875251</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
